--- a/Result/profitability/5234.xlsx
+++ b/Result/profitability/5234.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM64"/>
+  <dimension ref="A1:AM65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.84</v>
       </c>
       <c r="M2" t="n">
-        <v>1.80875</v>
+        <v>1.925</v>
       </c>
       <c r="N2" t="n">
-        <v>37.91625</v>
+        <v>38.645</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>2.42</v>
       </c>
       <c r="M3" t="n">
-        <v>1.94875</v>
+        <v>2.00875</v>
       </c>
       <c r="N3" t="n">
-        <v>36.6</v>
+        <v>37.24625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -8558,6 +8558,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>5234</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1282</v>
+      </c>
+      <c r="D65" t="n">
+        <v>732</v>
+      </c>
+      <c r="E65" t="n">
+        <v>550</v>
+      </c>
+      <c r="F65" t="n">
+        <v>42.91</v>
+      </c>
+      <c r="G65" t="n">
+        <v>257</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>20.09%</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>7</v>
+      </c>
+      <c r="J65" t="n">
+        <v>265</v>
+      </c>
+      <c r="K65" t="n">
+        <v>229</v>
+      </c>
+      <c r="L65" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.8575</v>
+      </c>
+      <c r="N65" t="n">
+        <v>40.405</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
+      </c>
+      <c r="V65" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0.009049773755656076</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>-0.1900000000000048</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>-0.0044083526682136</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>0.6799999999999999</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>0.4387096774193548</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>2.379999999999995</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>0.0587219343696026</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK65" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
